--- a/ch_05_statistical_testing_inference/ch_05_solution.xlsx
+++ b/ch_05_statistical_testing_inference/ch_05_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_05_statistical_testing_inference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_05_statistical_testing_inference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5A7E4B-3F58-4939-933C-5432E4823721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EA154-0954-4025-B5A5-832FECC9DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -52,13 +52,6 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -66,14 +59,21 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
+          <xlrd:rvb i="4"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
         </ext>
       </extLst>
     </bk>
@@ -103,7 +103,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -132,7 +132,7 @@
 pd.DataFrame({
     'Test statistic': [round(t_stat, 4)],
     'p-value': [round(p_value, 4)],
-    'Asia mean': [round(japan.mean(), 2)],
+    'Japan mean': [round(japan.mean(), 2)],
     'Europe mean': [round(europe.mean(), 2)],
     'Difference': [round(japan.mean() - europe.mean(), 2)]
 })</code>
@@ -1300,8 +1300,8 @@
       <xdr:rowOff>135467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>609601</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>585789</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>154617</xdr:rowOff>
     </xdr:to>
@@ -1349,7 +1349,7 @@
       <xdr:rowOff>118533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>441355</xdr:colOff>
       <xdr:row>91</xdr:row>
       <xdr:rowOff>127001</xdr:rowOff>
@@ -1433,29 +1433,171 @@
 </rvTypesInfo>
 </file>
 
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
+  <a r="12" c="10">
+    <v t="s"/>
+    <v t="s">mpg</v>
+    <v t="s">cylinders</v>
+    <v t="s">displacement</v>
+    <v t="s">horsepower</v>
+    <v t="s">weight</v>
+    <v t="s">acceleration</v>
+    <v t="s">model_year</v>
+    <v t="s">origin</v>
+    <v t="s">name</v>
+    <v>0</v>
+    <v>18</v>
+    <v>8</v>
+    <v>307</v>
+    <v>130</v>
+    <v>3504</v>
+    <v>12</v>
+    <v>70</v>
+    <v t="s">usa</v>
+    <v t="s">chevrolet chevelle malibu</v>
+    <v>1</v>
+    <v>15</v>
+    <v>8</v>
+    <v>350</v>
+    <v>165</v>
+    <v>3693</v>
+    <v>11.5</v>
+    <v>70</v>
+    <v t="s">usa</v>
+    <v t="s">buick skylark 320</v>
+    <v>2</v>
+    <v>18</v>
+    <v>8</v>
+    <v>318</v>
+    <v>150</v>
+    <v>3436</v>
+    <v>11</v>
+    <v>70</v>
+    <v t="s">usa</v>
+    <v t="s">plymouth satellite</v>
+    <v>3</v>
+    <v>16</v>
+    <v>8</v>
+    <v>304</v>
+    <v>150</v>
+    <v>3433</v>
+    <v>12</v>
+    <v>70</v>
+    <v t="s">usa</v>
+    <v t="s">amc rebel sst</v>
+    <v>4</v>
+    <v>17</v>
+    <v>8</v>
+    <v>302</v>
+    <v>140</v>
+    <v>3449</v>
+    <v>10.5</v>
+    <v>70</v>
+    <v t="s">usa</v>
+    <v t="s">ford torino</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v>393</v>
+    <v>27</v>
+    <v>4</v>
+    <v>140</v>
+    <v>86</v>
+    <v>2790</v>
+    <v>15.6</v>
+    <v>82</v>
+    <v t="s">usa</v>
+    <v t="s">ford mustang gl</v>
+    <v>394</v>
+    <v>44</v>
+    <v>4</v>
+    <v>97</v>
+    <v>52</v>
+    <v>2130</v>
+    <v>24.6</v>
+    <v>82</v>
+    <v t="s">europe</v>
+    <v t="s">vw pickup</v>
+    <v>395</v>
+    <v>32</v>
+    <v>4</v>
+    <v>135</v>
+    <v>84</v>
+    <v>2295</v>
+    <v>11.6</v>
+    <v>82</v>
+    <v t="s">usa</v>
+    <v t="s">dodge rampage</v>
+    <v>396</v>
+    <v>28</v>
+    <v>4</v>
+    <v>120</v>
+    <v>79</v>
+    <v>2625</v>
+    <v>18.600000000000001</v>
+    <v>82</v>
+    <v t="s">usa</v>
+    <v t="s">ford ranger</v>
+    <v>397</v>
+    <v>31</v>
+    <v>4</v>
+    <v>119</v>
+    <v>82</v>
+    <v>2720</v>
+    <v>19.399999999999999</v>
+    <v>82</v>
+    <v t="s">usa</v>
+    <v t="s">chevy s-10</v>
+  </a>
+</arrayData>
+</file>
+
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
-    <v>14</v>
+    <v>0</v>
   </rv>
   <rv s="1">
+    <v>DataFrame</v>
+    <v>1</v>
+    <v>0</v>
+  </rv>
+  <rv s="2">
+    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
+    <v>DataFrame</v>
+    <v xml:space="preserve">      mpg  cylinders  displacement  horsepower  weight  acceleration  \
+0    18.0          8         307.0       130.0    3504          12.0   
+1    15.0          8         350.0       165.0    3693          11.5   
+2    18.0          8         318.0  ...</v>
+    <v>1</v>
+    <v>2</v>
+  </rv>
+  <rv s="3">
     <fb>0</fb>
-    <v>0</v>
+    <v>3</v>
   </rv>
   <rv s="2">
     <fb>0</fb>
     <v>&lt;class 'NoneType'&gt;</v>
     <v>NoneType</v>
     <v>None</v>
-    <v>1</v>
-    <v>1</v>
+    <v>3</v>
+    <v>2</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
@@ -1464,12 +1606,14 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
-  <s t="_error">
-    <k n="errorType" t="i"/>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+  <s t="_array">
+    <k n="array" t="a"/>
   </s>
-  <s t="_formattednumber">
-    <k n="_Format" t="spb"/>
+  <s t="_entity">
+    <k n="_DisplayString" t="s"/>
+    <k n="_ViewInfo" t="spb"/>
+    <k n="arrayPreview" t="r"/>
   </s>
   <s t="_python">
     <k n="Python_type" t="s"/>
@@ -1477,6 +1621,9 @@
     <k n="Python_str" t="s"/>
     <k n="preview" t="r"/>
     <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_formattednumber">
+    <k n="_Format" t="spb"/>
   </s>
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
@@ -1488,28 +1635,48 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="2">
+  <spbData count="4">
     <spb s="0">
+      <v>398</v>
+      <v>9</v>
+      <v>DataFrame</v>
+      <v>arrayPreview</v>
       <v>1</v>
     </spb>
     <spb s="1">
+      <v>0</v>
+    </spb>
+    <spb s="2">
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
+    </spb>
+    <spb s="3">
+      <v>1</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="4">
   <s>
-    <k n="_Self" t="i"/>
+    <k n="drw" t="i"/>
+    <k n="dcol" t="i"/>
+    <k n="name" t="s"/>
+    <k n="array" t="s"/>
+    <k n="headers" t="b"/>
+  </s>
+  <s>
+    <k n="ArrayCardInfo" t="spb"/>
   </s>
   <s>
     <k n="link" t="s"/>
     <k n="logo" t="s"/>
     <k n="name" t="s"/>
+  </s>
+  <s>
+    <k n="_Self" t="i"/>
   </s>
 </spbStructures>
 </file>
@@ -1843,17 +2010,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K399"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.8203125" customWidth="1"/>
-    <col min="3" max="3" width="13.41015625" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
-    <col min="6" max="6" width="12.46875" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" customWidth="1"/>
-    <col min="9" max="9" width="30.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
+    <col min="9" max="9" width="30.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1881,12 +2048,12 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" cm="1">
-        <f t="array" aca="1" ref="K1" ca="1">_xlfn._xlws.PY(0,1,mpg[#All])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="K1" t="e" cm="1" vm="1">
+        <f t="array" ref="K1">_xlfn._xlws.PY(0,1,mpg[#All])</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -1915,7 +2082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -1944,7 +2111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -1973,7 +2140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -2002,7 +2169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -2031,7 +2198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2060,7 +2227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2089,7 +2256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2118,7 +2285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2147,7 +2314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2176,7 +2343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -2205,7 +2372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2234,7 +2401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -2263,7 +2430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2292,7 +2459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -2321,7 +2488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -2350,7 +2517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2379,7 +2546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2408,7 +2575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2437,7 +2604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -2466,7 +2633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2495,7 +2662,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2524,7 +2691,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2553,7 +2720,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2582,7 +2749,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2611,7 +2778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2640,7 +2807,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2669,7 +2836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2698,7 +2865,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2727,7 +2894,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2756,7 +2923,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2785,7 +2952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2814,7 +2981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2840,7 +3007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>19</v>
       </c>
@@ -2869,7 +3036,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -2898,7 +3065,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2927,7 +3094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>19</v>
       </c>
@@ -2956,7 +3123,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2985,7 +3152,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>14</v>
       </c>
@@ -3014,7 +3181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>14</v>
       </c>
@@ -3043,7 +3210,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3072,7 +3239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3101,7 +3268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>12</v>
       </c>
@@ -3130,7 +3297,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3159,7 +3326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3188,7 +3355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>18</v>
       </c>
@@ -3217,7 +3384,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>22</v>
       </c>
@@ -3246,7 +3413,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>19</v>
       </c>
@@ -3275,7 +3442,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>18</v>
       </c>
@@ -3304,7 +3471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>23</v>
       </c>
@@ -3333,7 +3500,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>28</v>
       </c>
@@ -3362,7 +3529,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>30</v>
       </c>
@@ -3391,7 +3558,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>30</v>
       </c>
@@ -3420,7 +3587,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>31</v>
       </c>
@@ -3449,7 +3616,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>35</v>
       </c>
@@ -3478,7 +3645,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3507,7 +3674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3536,7 +3703,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3565,7 +3732,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3594,7 +3761,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3623,7 +3790,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3652,7 +3819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3681,7 +3848,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3710,7 +3877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3739,7 +3906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3768,7 +3935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3797,7 +3964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3826,7 +3993,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3855,7 +4022,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>13</v>
       </c>
@@ -3884,7 +4051,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>12</v>
       </c>
@@ -3913,7 +4080,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>13</v>
       </c>
@@ -3942,7 +4109,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>19</v>
       </c>
@@ -3971,7 +4138,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>15</v>
       </c>
@@ -4000,7 +4167,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>13</v>
       </c>
@@ -4029,7 +4196,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>13</v>
       </c>
@@ -4058,7 +4225,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>14</v>
       </c>
@@ -4087,7 +4254,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>18</v>
       </c>
@@ -4116,7 +4283,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>22</v>
       </c>
@@ -4145,7 +4312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>21</v>
       </c>
@@ -4174,7 +4341,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>26</v>
       </c>
@@ -4203,7 +4370,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>22</v>
       </c>
@@ -4232,7 +4399,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>28</v>
       </c>
@@ -4261,7 +4428,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>23</v>
       </c>
@@ -4290,7 +4457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>28</v>
       </c>
@@ -4319,7 +4486,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>27</v>
       </c>
@@ -4348,7 +4515,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>13</v>
       </c>
@@ -4377,7 +4544,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>14</v>
       </c>
@@ -4406,7 +4573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -4435,7 +4602,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>14</v>
       </c>
@@ -4464,7 +4631,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>15</v>
       </c>
@@ -4493,7 +4660,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4522,7 +4689,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4551,7 +4718,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4580,7 +4747,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4609,7 +4776,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4638,7 +4805,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4667,7 +4834,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4696,7 +4863,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4725,7 +4892,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4754,7 +4921,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4783,7 +4950,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4812,7 +4979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4841,7 +5008,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>26</v>
       </c>
@@ -4870,7 +5037,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>11</v>
       </c>
@@ -4899,7 +5066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>12</v>
       </c>
@@ -4928,7 +5095,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>13</v>
       </c>
@@ -4957,7 +5124,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>12</v>
       </c>
@@ -4986,7 +5153,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>18</v>
       </c>
@@ -5015,7 +5182,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5044,7 +5211,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21</v>
       </c>
@@ -5073,7 +5240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>22</v>
       </c>
@@ -5102,7 +5269,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>18</v>
       </c>
@@ -5131,7 +5298,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>19</v>
       </c>
@@ -5160,7 +5327,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>21</v>
       </c>
@@ -5189,7 +5356,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>26</v>
       </c>
@@ -5218,7 +5385,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>15</v>
       </c>
@@ -5247,7 +5414,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>16</v>
       </c>
@@ -5276,7 +5443,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>29</v>
       </c>
@@ -5305,7 +5472,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5334,7 +5501,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5363,7 +5530,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>19</v>
       </c>
@@ -5392,7 +5559,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>15</v>
       </c>
@@ -5421,7 +5588,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>24</v>
       </c>
@@ -5450,7 +5617,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5479,7 +5646,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5508,7 +5675,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5537,7 +5704,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5563,7 +5730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5592,7 +5759,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5621,7 +5788,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5650,7 +5817,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5679,7 +5846,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5708,7 +5875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5737,7 +5904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5766,7 +5933,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5795,7 +5962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5824,7 +5991,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5853,7 +6020,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>13</v>
       </c>
@@ -5882,7 +6049,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>14</v>
       </c>
@@ -5911,7 +6078,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>14</v>
       </c>
@@ -5940,7 +6107,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>14</v>
       </c>
@@ -5969,7 +6136,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>29</v>
       </c>
@@ -5998,7 +6165,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>26</v>
       </c>
@@ -6027,7 +6194,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>26</v>
       </c>
@@ -6056,7 +6223,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31</v>
       </c>
@@ -6085,7 +6252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>32</v>
       </c>
@@ -6114,7 +6281,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>28</v>
       </c>
@@ -6143,7 +6310,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>24</v>
       </c>
@@ -6172,7 +6339,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>26</v>
       </c>
@@ -6201,7 +6368,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>24</v>
       </c>
@@ -6230,7 +6397,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>26</v>
       </c>
@@ -6259,7 +6426,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>31</v>
       </c>
@@ -6288,7 +6455,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>19</v>
       </c>
@@ -6317,7 +6484,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>18</v>
       </c>
@@ -6346,7 +6513,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>15</v>
       </c>
@@ -6375,7 +6542,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>15</v>
       </c>
@@ -6404,7 +6571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>16</v>
       </c>
@@ -6433,7 +6600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>15</v>
       </c>
@@ -6462,7 +6629,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>16</v>
       </c>
@@ -6491,7 +6658,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6520,7 +6687,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6549,7 +6716,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6578,7 +6745,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6607,7 +6774,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6636,7 +6803,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6665,7 +6832,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6694,7 +6861,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6723,7 +6890,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6752,7 +6919,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6781,7 +6948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6810,7 +6977,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6839,7 +7006,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>24</v>
       </c>
@@ -6868,7 +7035,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>25</v>
       </c>
@@ -6897,7 +7064,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>24</v>
       </c>
@@ -6926,7 +7093,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -6955,7 +7122,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>29</v>
       </c>
@@ -6984,7 +7151,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>19</v>
       </c>
@@ -7013,7 +7180,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>23</v>
       </c>
@@ -7042,7 +7209,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>23</v>
       </c>
@@ -7071,7 +7238,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>22</v>
       </c>
@@ -7100,7 +7267,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>25</v>
       </c>
@@ -7129,7 +7296,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>33</v>
       </c>
@@ -7158,7 +7325,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>28</v>
       </c>
@@ -7187,7 +7354,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>25</v>
       </c>
@@ -7216,7 +7383,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>25</v>
       </c>
@@ -7245,7 +7412,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26</v>
       </c>
@@ -7274,7 +7441,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>27</v>
       </c>
@@ -7303,7 +7470,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -7332,7 +7499,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>16</v>
       </c>
@@ -7361,7 +7528,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -7390,7 +7557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -7419,7 +7586,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>22</v>
       </c>
@@ -7448,7 +7615,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>22</v>
       </c>
@@ -7477,7 +7644,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7506,7 +7673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7535,7 +7702,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7564,7 +7731,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7593,7 +7760,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7622,7 +7789,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7651,7 +7818,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7680,7 +7847,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7709,7 +7876,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7738,7 +7905,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7767,7 +7934,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7796,7 +7963,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7825,7 +7992,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7854,7 +8021,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -7883,7 +8050,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20</v>
       </c>
@@ -7912,7 +8079,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>13</v>
       </c>
@@ -7941,7 +8108,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>19</v>
       </c>
@@ -7970,7 +8137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>19</v>
       </c>
@@ -7999,7 +8166,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -8028,7 +8195,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -8057,7 +8224,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>13</v>
       </c>
@@ -8086,7 +8253,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>13</v>
       </c>
@@ -8115,7 +8282,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>13</v>
       </c>
@@ -8144,7 +8311,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -8173,7 +8340,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>30</v>
       </c>
@@ -8202,7 +8369,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>36</v>
       </c>
@@ -8231,7 +8398,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -8260,7 +8427,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -8289,7 +8456,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -8318,7 +8485,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>17</v>
       </c>
@@ -8347,7 +8514,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -8376,7 +8543,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>15</v>
       </c>
@@ -8405,7 +8572,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -8434,7 +8601,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -8463,7 +8630,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>19</v>
       </c>
@@ -8492,7 +8659,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8521,7 +8688,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8550,7 +8717,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8579,7 +8746,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8608,7 +8775,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8637,7 +8804,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8666,7 +8833,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8695,7 +8862,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8724,7 +8891,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8753,7 +8920,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8782,7 +8949,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8811,7 +8978,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8840,7 +9007,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -8869,7 +9036,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>22</v>
       </c>
@@ -8898,7 +9065,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -8927,7 +9094,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -8956,7 +9123,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -8985,7 +9152,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -9014,7 +9181,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -9043,7 +9210,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -9072,7 +9239,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -9101,7 +9268,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -9130,7 +9297,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -9159,7 +9326,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -9188,7 +9355,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -9217,7 +9384,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -9246,7 +9413,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -9275,7 +9442,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -9304,7 +9471,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -9333,7 +9500,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -9362,7 +9529,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -9391,7 +9558,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -9420,7 +9587,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -9449,7 +9616,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -9478,7 +9645,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9507,7 +9674,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9536,7 +9703,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9565,7 +9732,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9594,7 +9761,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9623,7 +9790,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9652,7 +9819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9681,7 +9848,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9710,7 +9877,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9739,7 +9906,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9768,7 +9935,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9797,7 +9964,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9826,7 +9993,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9855,7 +10022,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>17</v>
       </c>
@@ -9884,7 +10051,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -9913,7 +10080,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -9942,7 +10109,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -9971,7 +10138,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -10000,7 +10167,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -10029,7 +10196,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -10058,7 +10225,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -10087,7 +10254,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -10116,7 +10283,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -10145,7 +10312,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10174,7 +10341,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -10203,7 +10370,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -10232,7 +10399,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -10261,7 +10428,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -10290,7 +10457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -10319,7 +10486,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -10348,7 +10515,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -10377,7 +10544,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -10406,7 +10573,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -10435,7 +10602,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -10464,7 +10631,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -10493,7 +10660,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10522,7 +10689,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10551,7 +10718,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10580,7 +10747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10609,7 +10776,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10638,7 +10805,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10667,7 +10834,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10696,7 +10863,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10725,7 +10892,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10754,7 +10921,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10783,7 +10950,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10812,7 +10979,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10841,7 +11008,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -10870,7 +11037,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -10899,7 +11066,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -10928,7 +11095,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -10957,7 +11124,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>28</v>
       </c>
@@ -10986,7 +11153,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -11015,7 +11182,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -11044,7 +11211,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -11073,7 +11240,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -11102,7 +11269,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -11131,7 +11298,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -11160,7 +11327,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>37</v>
       </c>
@@ -11189,7 +11356,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -11218,7 +11385,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -11247,7 +11414,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -11276,7 +11443,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -11305,7 +11472,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -11334,7 +11501,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -11363,7 +11530,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -11392,7 +11559,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>30</v>
       </c>
@@ -11421,7 +11588,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -11450,7 +11617,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -11476,7 +11643,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11505,7 +11672,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11534,7 +11701,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11563,7 +11730,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11592,7 +11759,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11621,7 +11788,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11647,7 +11814,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11676,7 +11843,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11705,7 +11872,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11734,7 +11901,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11763,7 +11930,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11792,7 +11959,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11821,7 +11988,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11850,7 +12017,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>39</v>
       </c>
@@ -11879,7 +12046,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -11908,7 +12075,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -11937,7 +12104,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>37</v>
       </c>
@@ -11966,7 +12133,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -11995,7 +12162,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -12024,7 +12191,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -12053,7 +12220,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -12082,7 +12249,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -12111,7 +12278,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>33</v>
       </c>
@@ -12140,7 +12307,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -12166,7 +12333,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -12195,7 +12362,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -12224,7 +12391,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -12253,7 +12420,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -12282,7 +12449,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -12311,7 +12478,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -12340,7 +12507,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -12369,7 +12536,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -12398,7 +12565,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -12427,7 +12594,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -12456,7 +12623,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -12485,7 +12652,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12514,7 +12681,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12543,7 +12710,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12572,7 +12739,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12601,7 +12768,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12630,7 +12797,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12659,7 +12826,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12688,7 +12855,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12717,7 +12884,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12743,7 +12910,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12772,7 +12939,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12801,7 +12968,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12830,7 +12997,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>38</v>
       </c>
@@ -12859,7 +13026,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>36</v>
       </c>
@@ -12888,7 +13055,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>36</v>
       </c>
@@ -12917,7 +13084,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>36</v>
       </c>
@@ -12946,7 +13113,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>34</v>
       </c>
@@ -12975,7 +13142,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>38</v>
       </c>
@@ -13004,7 +13171,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>32</v>
       </c>
@@ -13033,7 +13200,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>38</v>
       </c>
@@ -13062,7 +13229,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>25</v>
       </c>
@@ -13091,7 +13258,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>38</v>
       </c>
@@ -13120,7 +13287,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>26</v>
       </c>
@@ -13149,7 +13316,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>22</v>
       </c>
@@ -13178,7 +13345,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>32</v>
       </c>
@@ -13207,7 +13374,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>36</v>
       </c>
@@ -13236,7 +13403,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>27</v>
       </c>
@@ -13265,7 +13432,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>27</v>
       </c>
@@ -13294,7 +13461,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>44</v>
       </c>
@@ -13323,7 +13490,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>32</v>
       </c>
@@ -13352,7 +13519,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>28</v>
       </c>
@@ -13381,7 +13548,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>31</v>
       </c>
@@ -13421,209 +13588,155 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4BA3DC-CC7A-4BBE-90C7-63E4659EAB5B}">
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="1" max="1" width="16.87890625" customWidth="1"/>
-    <col min="2" max="2" width="12.52734375" customWidth="1"/>
-    <col min="3" max="4" width="17.234375" customWidth="1"/>
-    <col min="5" max="5" width="11.29296875" customWidth="1"/>
-    <col min="6" max="6" width="5.234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.3515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.8203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.234375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="11.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1:I5" ca="1">_xlfn._xlws.PY(1,0)</f>
+        <f t="array" ref="A1:I5">_xlfn._xlws.PY(1,0)</f>
         <v/>
       </c>
       <c r="B1" t="str">
-        <f ca="1"/>
         <v>count</v>
       </c>
       <c r="C1" s="1" t="str">
-        <f ca="1"/>
         <v>mean</v>
       </c>
       <c r="D1" s="1" t="str">
-        <f ca="1"/>
         <v>std</v>
       </c>
       <c r="E1" s="1" t="str">
-        <f ca="1"/>
         <v>min</v>
       </c>
       <c r="F1" s="1" t="str">
-        <f ca="1"/>
         <v>25%</v>
       </c>
       <c r="G1" s="1" t="str">
-        <f ca="1"/>
         <v>50%</v>
       </c>
       <c r="H1" s="1" t="str">
-        <f ca="1"/>
         <v>75%</v>
       </c>
       <c r="I1" s="1" t="str">
-        <f ca="1"/>
         <v>max</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
-        <f ca="1"/>
         <v>origin</v>
       </c>
       <c r="B2" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="C2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="D2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="E2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="F2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="G2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="H2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="I2" s="1" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B3">
-        <f ca="1"/>
         <v>70</v>
       </c>
       <c r="C3" s="1">
-        <f ca="1"/>
         <v>27.89142857142857</v>
       </c>
       <c r="D3" s="1">
-        <f ca="1"/>
         <v>6.7239296407431706</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1"/>
         <v>16.2</v>
       </c>
       <c r="F3" s="1">
-        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="G3" s="1">
-        <f ca="1"/>
         <v>26.5</v>
       </c>
       <c r="H3" s="1">
-        <f ca="1"/>
         <v>30.65</v>
       </c>
       <c r="I3" s="1">
-        <f ca="1"/>
         <v>44.3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B4">
-        <f ca="1"/>
         <v>79</v>
       </c>
       <c r="C4" s="1">
-        <f ca="1"/>
         <v>30.450632911392404</v>
       </c>
       <c r="D4" s="1">
-        <f ca="1"/>
         <v>6.0900480697383239</v>
       </c>
       <c r="E4" s="1">
-        <f ca="1"/>
         <v>18</v>
       </c>
       <c r="F4" s="1">
-        <f ca="1"/>
         <v>25.7</v>
       </c>
       <c r="G4" s="1">
-        <f ca="1"/>
         <v>31.6</v>
       </c>
       <c r="H4" s="1">
-        <f ca="1"/>
         <v>34.049999999999997</v>
       </c>
       <c r="I4" s="1">
-        <f ca="1"/>
         <v>46.6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B5">
-        <f ca="1"/>
         <v>249</v>
       </c>
       <c r="C5" s="1">
-        <f ca="1"/>
         <v>20.083534136546184</v>
       </c>
       <c r="D5" s="1">
-        <f ca="1"/>
         <v>6.4028920160496918</v>
       </c>
       <c r="E5" s="1">
-        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="F5" s="1">
-        <f ca="1"/>
         <v>15</v>
       </c>
       <c r="G5" s="1">
-        <f ca="1"/>
         <v>18.5</v>
       </c>
       <c r="H5" s="1">
-        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="I5" s="1">
-        <f ca="1"/>
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -13632,634 +13745,509 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="str" cm="1">
-        <f t="array" aca="1" ref="A8:E9" ca="1">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" ref="A8:E9">_xlfn._xlws.PY(2,0)</f>
         <v>Test statistic</v>
       </c>
       <c r="B8" t="str">
-        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C8" t="str">
-        <f ca="1"/>
-        <v>Asia mean</v>
+        <v>Japan mean</v>
       </c>
       <c r="D8" t="str">
-        <f ca="1"/>
         <v>Europe mean</v>
       </c>
       <c r="E8" t="str">
-        <f ca="1"/>
         <v>Difference</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9">
-        <f ca="1"/>
         <v>2.4378000000000002</v>
       </c>
       <c r="B9">
-        <f ca="1"/>
         <v>1.6E-2</v>
       </c>
       <c r="C9">
-        <f ca="1"/>
         <v>30.45</v>
       </c>
       <c r="D9">
-        <f ca="1"/>
         <v>27.89</v>
       </c>
       <c r="E9">
-        <f ca="1"/>
         <v>2.56</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="str" cm="1">
-        <f t="array" aca="1" ref="A12" ca="1">_xlfn._xlws.PY(3,0)</f>
+        <f t="array" ref="A12">_xlfn._xlws.PY(3,0)</f>
         <v>Cohen's d (effect size): 0.4002</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="str" cm="1">
-        <f t="array" aca="1" ref="A14:E15" ca="1">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" ref="A14:E15">_xlfn._xlws.PY(4,0)</f>
         <v>F-statistic</v>
       </c>
       <c r="B14" t="str">
-        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C14" t="str">
-        <f ca="1"/>
         <v>USA mean</v>
       </c>
       <c r="D14" t="str">
-        <f ca="1"/>
         <v>Europe mean</v>
       </c>
       <c r="E14" t="str">
-        <f ca="1"/>
         <v>Japan mean</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15">
-        <f ca="1"/>
         <v>98.54</v>
       </c>
       <c r="B15" t="str">
-        <f ca="1"/>
         <v>0.0</v>
       </c>
       <c r="C15">
-        <f ca="1"/>
         <v>20.079999999999998</v>
       </c>
       <c r="D15">
-        <f ca="1"/>
         <v>27.89</v>
       </c>
       <c r="E15">
-        <f ca="1"/>
         <v>30.45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="str" cm="1">
-        <f t="array" aca="1" ref="A17:G20" ca="1">_xlfn._xlws.PY(5,0)</f>
+        <f t="array" ref="A17:G20">_xlfn._xlws.PY(5,0)</f>
         <v>group1</v>
       </c>
       <c r="B17" t="str">
-        <f ca="1"/>
         <v>group2</v>
       </c>
       <c r="C17" t="str">
-        <f ca="1"/>
         <v>meandiff</v>
       </c>
       <c r="D17" t="str">
-        <f ca="1"/>
         <v>p-adj</v>
       </c>
       <c r="E17" t="str">
-        <f ca="1"/>
         <v>lower</v>
       </c>
       <c r="F17" t="str">
-        <f ca="1"/>
         <v>upper</v>
       </c>
       <c r="G17" t="str">
-        <f ca="1"/>
         <v>reject</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B18" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="C18">
-        <f ca="1"/>
         <v>2.5592000000000001</v>
       </c>
       <c r="D18">
-        <f ca="1"/>
         <v>4.0399999999999998E-2</v>
       </c>
       <c r="E18">
-        <f ca="1"/>
         <v>8.77E-2</v>
       </c>
       <c r="F18">
-        <f ca="1"/>
         <v>5.0307000000000004</v>
       </c>
       <c r="G18" t="b">
-        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B19" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="C19">
-        <f ca="1"/>
         <v>-7.8079000000000001</v>
       </c>
       <c r="D19">
-        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="E19">
-        <f ca="1"/>
         <v>-9.8447999999999993</v>
       </c>
       <c r="F19">
-        <f ca="1"/>
         <v>-5.7709999999999999</v>
       </c>
       <c r="G19" t="b">
-        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B20" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="C20">
-        <f ca="1"/>
         <v>-10.367100000000001</v>
       </c>
       <c r="D20">
-        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="E20">
-        <f ca="1"/>
         <v>-12.311400000000001</v>
       </c>
       <c r="F20">
-        <f ca="1"/>
         <v>-8.4228000000000005</v>
       </c>
       <c r="G20" t="b">
-        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="str" cm="1">
-        <f t="array" aca="1" ref="A23:D32" ca="1">_xlfn._xlws.PY(6,0)</f>
+        <f t="array" ref="A23:D32">_xlfn._xlws.PY(6,0)</f>
         <v>origin</v>
       </c>
       <c r="B23" t="str">
-        <f ca="1"/>
         <v>cylinders</v>
       </c>
       <c r="C23" t="str">
-        <f ca="1"/>
         <v>engine_size</v>
       </c>
       <c r="D23" t="str">
-        <f ca="1"/>
         <v>count</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B24">
-        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="C24" t="str">
-        <f ca="1"/>
         <v>Large (8)</v>
       </c>
       <c r="D24">
-        <f ca="1"/>
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B25">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C25" t="str">
-        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D25">
-        <f ca="1"/>
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B26">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C26" t="str">
-        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D26">
-        <f ca="1"/>
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B27">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C27" t="str">
-        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D27">
-        <f ca="1"/>
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B28">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C28" t="str">
-        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D28">
-        <f ca="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B29">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C29" t="str">
-        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D29">
-        <f ca="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B30">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C30" t="str">
-        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D30">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B31">
-        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="C31" t="str">
-        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D31">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B32">
-        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="C32" t="str">
-        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D32">
-        <f ca="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="str" cm="1">
-        <f t="array" aca="1" ref="A34:D38" ca="1">_xlfn._xlws.PY(7,0)</f>
+        <f t="array" ref="A34:D38">_xlfn._xlws.PY(7,0)</f>
         <v>engine_size</v>
       </c>
       <c r="B34" t="str">
-        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="C34" t="str">
-        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D34" t="str">
-        <f ca="1"/>
         <v>Large (8)</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
-        <f ca="1"/>
         <v>origin</v>
       </c>
       <c r="B35" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="C35" t="str">
-        <f ca="1"/>
         <v/>
       </c>
       <c r="D35" t="str">
-        <f ca="1"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
-        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B36">
-        <f ca="1"/>
         <v>63</v>
       </c>
       <c r="C36">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="D36">
-        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
-        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B37">
-        <f ca="1"/>
         <v>73</v>
       </c>
       <c r="C37">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="D37">
-        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
-        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B38">
-        <f ca="1"/>
         <v>72</v>
       </c>
       <c r="C38">
-        <f ca="1"/>
         <v>74</v>
       </c>
       <c r="D38">
-        <f ca="1"/>
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="str" cm="1">
-        <f t="array" aca="1" ref="A42:C43" ca="1">_xlfn._xlws.PY(8,0)</f>
+        <f t="array" ref="A42:C43">_xlfn._xlws.PY(8,0)</f>
         <v>Chi-square statistic</v>
       </c>
       <c r="B42" t="str">
-        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C42" t="str">
-        <f ca="1"/>
         <v>Degrees of freedom</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
-        <f ca="1"/>
         <v>149.93</v>
       </c>
       <c r="B43" t="str">
-        <f ca="1"/>
         <v>0.0</v>
       </c>
       <c r="C43">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="str" cm="1">
-        <f t="array" aca="1" ref="A47" ca="1">_xlfn._xlws.PY(9,0)</f>
+        <f t="array" ref="A47">_xlfn._xlws.PY(9,0)</f>
         <v>Cramér's V: 0.43</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" cm="1" vm="2">
-        <f t="array" aca="1" ref="A51" ca="1">_xlfn._xlws.PY(10,1)</f>
+        <f t="array" ref="A51">_xlfn._xlws.PY(10,1)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="str" cm="1">
-        <f t="array" aca="1" ref="A53:D54" ca="1">_xlfn._xlws.PY(11,0)</f>
+        <f t="array" ref="A53:D54">_xlfn._xlws.PY(11,0)</f>
         <v>Original mean</v>
       </c>
       <c r="B53" t="str">
-        <f ca="1"/>
         <v>95% CI lower</v>
       </c>
       <c r="C53" t="str">
-        <f ca="1"/>
         <v>95% CI upper</v>
       </c>
       <c r="D53" t="str">
-        <f ca="1"/>
         <v>CI width</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54">
-        <f ca="1"/>
         <v>30.45</v>
       </c>
       <c r="B54">
-        <f ca="1"/>
         <v>29.08</v>
       </c>
       <c r="C54">
-        <f ca="1"/>
         <v>31.94</v>
       </c>
       <c r="D54">
-        <f ca="1"/>
         <v>2.86</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="e" cm="1" vm="3">
-        <f t="array" aca="1" ref="A57" ca="1">_xlfn._xlws.PY(12,0)</f>
+        <f t="array" ref="A57">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="str" cm="1">
-        <f t="array" aca="1" ref="A71:D73" ca="1">_xlfn._xlws.PY(13,0)</f>
+        <f t="array" ref="A71:D73">_xlfn._xlws.PY(13,0)</f>
         <v>Group</v>
       </c>
       <c r="B71" t="str">
-        <f ca="1"/>
         <v>Mean</v>
       </c>
       <c r="C71" t="str">
-        <f ca="1"/>
         <v>CI Lower (2.5%)</v>
       </c>
       <c r="D71" t="str">
-        <f ca="1"/>
         <v>CI Upper (97.5%)</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="str">
-        <f ca="1"/>
         <v>Japan</v>
       </c>
       <c r="B72" s="1">
-        <f ca="1"/>
         <v>30.450632911392404</v>
       </c>
       <c r="C72" s="1">
-        <f ca="1"/>
         <v>29.232120253164553</v>
       </c>
       <c r="D72" s="1">
-        <f ca="1"/>
         <v>31.810158227848103</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="str">
-        <f ca="1"/>
         <v>Europe</v>
       </c>
       <c r="B73" s="1">
-        <f ca="1"/>
         <v>27.89142857142857</v>
       </c>
       <c r="C73" s="1">
-        <f ca="1"/>
         <v>26.298464285714289</v>
       </c>
       <c r="D73" s="1">
-        <f ca="1"/>
         <v>29.408678571428577</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" t="e" cm="1" vm="4">
-        <f t="array" aca="1" ref="A79" ca="1">_xlfn._xlws.PY(14,0)</f>
+        <f t="array" ref="A79">_xlfn._xlws.PY(14,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>